--- a/MainTop/25.06.2026 Макс Озон/print_print_sorted.xlsx
+++ b/MainTop/25.06.2026 Макс Озон/print_print_sorted.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\25.06.2026 Макс Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9937967-48D0-47B7-B2C3-C5C70013FAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BFE8411-7A24-4EA3-BDC7-642F5310DB8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
